--- a/output/材料成型技术_2025-2026-1/05_课程目标结果表.xlsx
+++ b/output/材料成型技术_2025-2026-1/05_课程目标结果表.xlsx
@@ -635,11 +635,11 @@
         <v>0.652</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -732,7 +732,7 @@
         <v>0.744</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -829,11 +829,11 @@
         <v>0.656</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>0.8640000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1120,11 +1120,11 @@
         <v>0.68</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1217,7 +1217,7 @@
         <v>0.8120000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>0.576</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>0.76</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>0.772</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>0.704</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>0.756</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>0.712</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>0.8480000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2090,11 +2090,11 @@
         <v>0.6880000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2187,7 +2187,7 @@
         <v>0.8320000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>0.76</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>0.756</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2478,11 +2478,11 @@
         <v>0.6759999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -2575,7 +2575,7 @@
         <v>0.712</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2672,11 +2672,11 @@
         <v>0.6679999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -2769,11 +2769,11 @@
         <v>0.6960000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -2866,11 +2866,11 @@
         <v>0.6840000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -2963,7 +2963,7 @@
         <v>0.8440000000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3060,11 +3060,11 @@
         <v>0.616</v>
       </c>
       <c r="V27" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -3157,7 +3157,7 @@
         <v>0.536</v>
       </c>
       <c r="V28" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>0.452</v>
       </c>
       <c r="V29" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>0.764</v>
       </c>
       <c r="V30" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>0.736</v>
       </c>
       <c r="V31" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3545,11 +3545,11 @@
         <v>0.6759999999999999</v>
       </c>
       <c r="V32" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -3642,11 +3642,11 @@
         <v>0.6879999999999999</v>
       </c>
       <c r="V33" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -3739,11 +3739,11 @@
         <v>0.68</v>
       </c>
       <c r="V34" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -3836,7 +3836,7 @@
         <v>0.708</v>
       </c>
       <c r="V35" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -3933,11 +3933,11 @@
         <v>0.6679999999999999</v>
       </c>
       <c r="V36" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -4030,7 +4030,7 @@
         <v>0.376</v>
       </c>
       <c r="V37" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>0.9120000000000001</v>
       </c>
       <c r="V38" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>0.74</v>
       </c>
       <c r="V39" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>0.868</v>
       </c>
       <c r="V40" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>0.796</v>
       </c>
       <c r="V41" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -4515,11 +4515,11 @@
         <v>0.696</v>
       </c>
       <c r="V42" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -4612,11 +4612,11 @@
         <v>0.6200000000000001</v>
       </c>
       <c r="V43" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -4709,7 +4709,7 @@
         <v>0.732</v>
       </c>
       <c r="V44" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -4806,11 +4806,11 @@
         <v>0.664</v>
       </c>
       <c r="V45" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -4903,7 +4903,7 @@
         <v>0.804</v>
       </c>
       <c r="V46" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>0.336</v>
       </c>
       <c r="V47" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -5097,11 +5097,11 @@
         <v>0.6919999999999999</v>
       </c>
       <c r="V48" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -5194,7 +5194,7 @@
         <v>0.804</v>
       </c>
       <c r="V49" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>0.756</v>
       </c>
       <c r="V50" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>0.712</v>
       </c>
       <c r="V51" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>0.416</v>
       </c>
       <c r="V52" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -5582,11 +5582,11 @@
         <v>0.6880000000000001</v>
       </c>
       <c r="V53" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -5679,11 +5679,11 @@
         <v>0.6839999999999999</v>
       </c>
       <c r="V54" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
@@ -5776,7 +5776,7 @@
         <v>0.708</v>
       </c>
       <c r="V55" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>0.712</v>
       </c>
       <c r="V56" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -5970,11 +5970,11 @@
         <v>0.656</v>
       </c>
       <c r="V57" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -6067,11 +6067,11 @@
         <v>0.648</v>
       </c>
       <c r="V58" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -6164,11 +6164,11 @@
         <v>0.6160000000000001</v>
       </c>
       <c r="V59" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -6261,7 +6261,7 @@
         <v>0.736</v>
       </c>
       <c r="V60" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -6358,11 +6358,11 @@
         <v>0.624</v>
       </c>
       <c r="V61" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
@@ -6455,11 +6455,11 @@
         <v>0.6120000000000001</v>
       </c>
       <c r="V62" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
@@ -6552,11 +6552,11 @@
         <v>0.6439999999999999</v>
       </c>
       <c r="V63" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -6649,7 +6649,7 @@
         <v>0.724</v>
       </c>
       <c r="V64" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>0.8560000000000001</v>
       </c>
       <c r="V66" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -6940,11 +6940,11 @@
         <v>0.6560000000000001</v>
       </c>
       <c r="V67" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -7037,11 +7037,11 @@
         <v>0.68</v>
       </c>
       <c r="V68" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -7134,7 +7134,7 @@
         <v>0.732</v>
       </c>
       <c r="V69" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>0.704</v>
       </c>
       <c r="V70" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>0.752</v>
       </c>
       <c r="V71" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W71" t="inlineStr">
         <is>
@@ -7425,11 +7425,11 @@
         <v>0.6839999999999999</v>
       </c>
       <c r="V72" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
@@ -7522,11 +7522,11 @@
         <v>0.6799999999999999</v>
       </c>
       <c r="V73" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
@@ -7619,7 +7619,7 @@
         <v>0.704</v>
       </c>
       <c r="V74" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W74" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>0.8160000000000001</v>
       </c>
       <c r="V75" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W75" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>0</v>
       </c>
       <c r="V76" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W76" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>0.5840000000000001</v>
       </c>
       <c r="V77" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W77" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>0.8759999999999999</v>
       </c>
       <c r="V78" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W78" t="inlineStr">
         <is>
@@ -8104,11 +8104,11 @@
         <v>0.624</v>
       </c>
       <c r="V79" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
@@ -8201,7 +8201,7 @@
         <v>0.716</v>
       </c>
       <c r="V80" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W80" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>0.716</v>
       </c>
       <c r="V81" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W81" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>0.76</v>
       </c>
       <c r="V82" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W82" t="inlineStr">
         <is>
@@ -8492,11 +8492,11 @@
         <v>0.68</v>
       </c>
       <c r="V83" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
@@ -8589,11 +8589,11 @@
         <v>0.6840000000000001</v>
       </c>
       <c r="V84" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
@@ -8686,7 +8686,7 @@
         <v>0.72</v>
       </c>
       <c r="V85" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>0.864</v>
       </c>
       <c r="V86" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W86" t="inlineStr">
         <is>
@@ -8880,11 +8880,11 @@
         <v>0.68</v>
       </c>
       <c r="V87" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
@@ -8977,7 +8977,7 @@
         <v>0.4319999999999999</v>
       </c>
       <c r="V88" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W88" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>0.472</v>
       </c>
       <c r="V89" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W89" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>0.724</v>
       </c>
       <c r="V90" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W90" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>0.7</v>
       </c>
       <c r="V91" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W91" t="inlineStr">
         <is>
@@ -9365,11 +9365,11 @@
         <v>0.648</v>
       </c>
       <c r="V92" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
@@ -9462,7 +9462,7 @@
         <v>0.7</v>
       </c>
       <c r="V93" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W93" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>0.8</v>
       </c>
       <c r="V94" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W94" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>0.76</v>
       </c>
       <c r="V95" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W95" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>0.732</v>
       </c>
       <c r="V96" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W96" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>0.384</v>
       </c>
       <c r="V97" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W97" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>0.9320000000000001</v>
       </c>
       <c r="V98" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W98" t="inlineStr">
         <is>
@@ -10044,11 +10044,11 @@
         <v>0.652</v>
       </c>
       <c r="V99" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">
@@ -10141,7 +10141,7 @@
         <v>0.8759999999999999</v>
       </c>
       <c r="V100" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W100" t="inlineStr">
         <is>
@@ -10238,11 +10238,11 @@
         <v>0.616</v>
       </c>
       <c r="V101" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
@@ -10335,7 +10335,7 @@
         <v>0.708</v>
       </c>
       <c r="V102" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W102" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>0.5720000000000001</v>
       </c>
       <c r="V103" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W103" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>0.724</v>
       </c>
       <c r="V104" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W104" t="inlineStr">
         <is>
@@ -10626,11 +10626,11 @@
         <v>0.616</v>
       </c>
       <c r="V105" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
@@ -10723,7 +10723,7 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="V106" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W106" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>0.344</v>
       </c>
       <c r="V107" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W107" t="inlineStr">
         <is>
@@ -10917,11 +10917,11 @@
         <v>0.6960000000000001</v>
       </c>
       <c r="V108" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
@@ -11014,7 +11014,7 @@
         <v>0.796</v>
       </c>
       <c r="V109" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W109" t="inlineStr">
         <is>
@@ -11111,11 +11111,11 @@
         <v>0.664</v>
       </c>
       <c r="V110" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X110" t="inlineStr">
@@ -11208,11 +11208,11 @@
         <v>0.656</v>
       </c>
       <c r="V111" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
@@ -11305,7 +11305,7 @@
         <v>0.42</v>
       </c>
       <c r="V112" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W112" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>0.728</v>
       </c>
       <c r="V113" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W113" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>0.8240000000000001</v>
       </c>
       <c r="V114" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W114" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>0.728</v>
       </c>
       <c r="V115" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W115" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>0.788</v>
       </c>
       <c r="V116" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W116" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>0.8240000000000001</v>
       </c>
       <c r="V117" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W117" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>0.764</v>
       </c>
       <c r="V118" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W118" t="inlineStr">
         <is>
@@ -11984,11 +11984,11 @@
         <v>0.656</v>
       </c>
       <c r="V119" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
@@ -12081,11 +12081,11 @@
         <v>0.6719999999999999</v>
       </c>
       <c r="V120" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
@@ -12178,7 +12178,7 @@
         <v>0.5800000000000001</v>
       </c>
       <c r="V121" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W121" t="inlineStr">
         <is>
@@ -12378,14 +12378,14 @@
         <v>0.6728666666666666</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="O2" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -12461,14 +12461,14 @@
         <v>0.6692666666666666</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="Q3" t="n">
